--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N104_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N104_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.12185882649025</v>
+        <v>10.58230205930467</v>
       </c>
       <c r="D2" t="n">
-        <v>21.41121371670684</v>
+        <v>3.479322228964862</v>
       </c>
       <c r="E2" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F2" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.23761429952848</v>
+        <v>7.351112323673378</v>
       </c>
       <c r="D3" t="n">
-        <v>29.81784852971659</v>
+        <v>4.845400386078945</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F3" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.96800706403612</v>
+        <v>8.282301147905871</v>
       </c>
       <c r="D4" t="n">
-        <v>12.57436548838953</v>
+        <v>2.043334391863298</v>
       </c>
       <c r="E4" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F4" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.11525821401969</v>
+        <v>9.9312294597782</v>
       </c>
       <c r="D5" t="n">
-        <v>4.376514951634016</v>
+        <v>0.7111836796405276</v>
       </c>
       <c r="E5" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F5" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.20577685698309</v>
+        <v>11.08343873925975</v>
       </c>
       <c r="D6" t="n">
-        <v>67.83394582023203</v>
+        <v>11.02301619578771</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F6" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.23990184141451</v>
+        <v>7.026484049229857</v>
       </c>
       <c r="D7" t="n">
-        <v>22.02609772885545</v>
+        <v>3.579240880939011</v>
       </c>
       <c r="E7" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F7" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.97042492768736</v>
+        <v>10.0701940507492</v>
       </c>
       <c r="D8" t="n">
-        <v>25.97587594036245</v>
+        <v>4.221079840308898</v>
       </c>
       <c r="E8" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F8" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>72.91047573056711</v>
+        <v>11.84795230621716</v>
       </c>
       <c r="D9" t="n">
-        <v>71.74610207908113</v>
+        <v>11.65874158785068</v>
       </c>
       <c r="E9" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F9" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.48167762884893</v>
+        <v>2.515772614687952</v>
       </c>
       <c r="D10" t="n">
-        <v>15.00966355385756</v>
+        <v>2.439070327501853</v>
       </c>
       <c r="E10" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F10" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>71.78940077831173</v>
+        <v>11.66577762647566</v>
       </c>
       <c r="D11" t="n">
-        <v>69.62737258558859</v>
+        <v>11.31444804515815</v>
       </c>
       <c r="E11" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F11" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.22923323228858</v>
+        <v>4.099750400246895</v>
       </c>
       <c r="D12" t="n">
-        <v>28.18793052491397</v>
+        <v>4.580538710298519</v>
       </c>
       <c r="E12" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F12" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.94311462004237</v>
+        <v>2.590756125756885</v>
       </c>
       <c r="D13" t="n">
-        <v>14.51883615194123</v>
+        <v>2.35931087469045</v>
       </c>
       <c r="E13" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F13" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.30967471770361</v>
+        <v>10.28782214162684</v>
       </c>
       <c r="D14" t="n">
-        <v>59.1286095039347</v>
+        <v>9.60839904438939</v>
       </c>
       <c r="E14" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F14" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.99913738193229</v>
+        <v>4.062359824563996</v>
       </c>
       <c r="D15" t="n">
-        <v>14.99986961254387</v>
+        <v>2.437478812038379</v>
       </c>
       <c r="E15" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F15" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.59467479508685</v>
+        <v>7.409134654201613</v>
       </c>
       <c r="D16" t="n">
-        <v>45.69748668479053</v>
+        <v>7.425841586278461</v>
       </c>
       <c r="E16" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F16" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>70.19541270998616</v>
+        <v>11.40675456537275</v>
       </c>
       <c r="D17" t="n">
-        <v>64.29431719129906</v>
+        <v>10.4478265435861</v>
       </c>
       <c r="E17" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F17" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>61.24308123121407</v>
+        <v>9.952000700072286</v>
       </c>
       <c r="D18" t="n">
-        <v>60.9029273451417</v>
+        <v>9.896725693585527</v>
       </c>
       <c r="E18" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F18" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>64.89308821205341</v>
+        <v>10.54512683445868</v>
       </c>
       <c r="D19" t="n">
-        <v>57.61575154993545</v>
+        <v>9.362559626864511</v>
       </c>
       <c r="E19" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F19" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>40.74359966571136</v>
+        <v>6.620834945678096</v>
       </c>
       <c r="D20" t="n">
-        <v>37.2545309182868</v>
+        <v>6.053861274221606</v>
       </c>
       <c r="E20" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F20" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>40.54257713298249</v>
+        <v>6.588168784109656</v>
       </c>
       <c r="D21" t="n">
-        <v>29.25410044060812</v>
+        <v>4.753791321598819</v>
       </c>
       <c r="E21" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F21" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>56.03912290972577</v>
+        <v>9.106357472830437</v>
       </c>
       <c r="D22" t="n">
-        <v>51.70915404281784</v>
+        <v>8.4027375319579</v>
       </c>
       <c r="E22" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F22" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>56.34165872912463</v>
+        <v>9.155519543482752</v>
       </c>
       <c r="D23" t="n">
-        <v>50.47835237202644</v>
+        <v>8.202732260454296</v>
       </c>
       <c r="E23" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F23" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>48.82257599741805</v>
+        <v>7.933668599580433</v>
       </c>
       <c r="D24" t="n">
-        <v>37.42856442542471</v>
+        <v>6.082141719131515</v>
       </c>
       <c r="E24" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F24" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>48.72977783501683</v>
+        <v>7.918588898190235</v>
       </c>
       <c r="D25" t="n">
-        <v>37.35365299754662</v>
+        <v>6.069968612101325</v>
       </c>
       <c r="E25" t="n">
-        <v>16.68192277853126</v>
+        <v>2.71081245151133</v>
       </c>
       <c r="F25" t="n">
-        <v>20.17496745081854</v>
+        <v>3.278432210758013</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
